--- a/LubanConfig/MiniTemplate/Datas/基础数据/#角色技能数据表.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/基础数据/#角色技能数据表.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="46">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -180,6 +180,10 @@
   </si>
   <si>
     <t>map,int,角色技能倍率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弓</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -563,7 +567,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="9" style="2"/>
@@ -931,7 +935,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="3:9" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:9" ht="15.75" x14ac:dyDescent="0.2">
       <c r="C17" s="3">
         <v>12</v>
       </c>
@@ -954,7 +958,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="3:9" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:9" ht="15.75" x14ac:dyDescent="0.2">
       <c r="C18" s="3">
         <v>15</v>
       </c>
@@ -975,6 +979,170 @@
       </c>
       <c r="I18" s="4" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="3">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5">
+        <v>1</v>
+      </c>
+      <c r="F19" s="5">
+        <v>1</v>
+      </c>
+      <c r="G19" s="5">
+        <v>2</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="C20" s="3">
+        <v>3</v>
+      </c>
+      <c r="D20" s="5">
+        <v>1</v>
+      </c>
+      <c r="E20" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F20" s="5">
+        <v>1</v>
+      </c>
+      <c r="G20" s="5">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="C21" s="3">
+        <v>5</v>
+      </c>
+      <c r="D21" s="5">
+        <v>1</v>
+      </c>
+      <c r="E21" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="F21" s="5">
+        <v>1</v>
+      </c>
+      <c r="G21" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="C22" s="3">
+        <v>7</v>
+      </c>
+      <c r="D22" s="5">
+        <v>1</v>
+      </c>
+      <c r="E22" s="5">
+        <v>1</v>
+      </c>
+      <c r="F22" s="5">
+        <v>1</v>
+      </c>
+      <c r="G22" s="5">
+        <v>1.5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="C23" s="3">
+        <v>9</v>
+      </c>
+      <c r="D23" s="5">
+        <v>1</v>
+      </c>
+      <c r="E23" s="5">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="F23" s="5">
+        <v>1</v>
+      </c>
+      <c r="G23" s="5">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="C24" s="3">
+        <v>12</v>
+      </c>
+      <c r="D24" s="5">
+        <v>1</v>
+      </c>
+      <c r="E24" s="5">
+        <v>1</v>
+      </c>
+      <c r="F24" s="5">
+        <v>1</v>
+      </c>
+      <c r="G24" s="5">
+        <v>1.25</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="C25" s="3">
+        <v>15</v>
+      </c>
+      <c r="D25" s="5">
+        <v>1</v>
+      </c>
+      <c r="E25" s="5">
+        <v>1</v>
+      </c>
+      <c r="F25" s="5">
+        <v>1</v>
+      </c>
+      <c r="G25" s="5">
+        <v>1.67</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
